--- a/results/job_matches_2026-09-19.xlsx
+++ b/results/job_matches_2026-09-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Regal Entertainment Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3256e545b105e3</t>
+          <t>https://www.indeed.com/viewjob?jk=695e1a6790e5d227</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e679dbd4f0dd48e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc628f7d74985c07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4702034dd003ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=d1b682d21992aa0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, dbt, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,392 +601,252 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1889e38b8bdd30</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c291a59e036015</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>OCTO ETL Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7016138149863f08</t>
+          <t>https://www.indeed.com/viewjob?jk=7034ddc05a5e196a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III- AI &amp; Engineering/Software as a Service</t>
+          <t>Senior ML Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Kinesis, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10dde96050d4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=41542c40ed442d87</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Core Platforms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4534e033543a707</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9869546b3cb88f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdea1b0ba7904f76</t>
+          <t>https://www.indeed.com/viewjob?jk=df94682d2c3c155f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cambridge Investment Research, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Azure, Event Hubs, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc9568d9ed2024</t>
+          <t>https://www.indeed.com/viewjob?jk=20b168d606de0f06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud &amp; Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11340d96f177ca10</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe21468764e4ff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Applied Machine Learning Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Scala, Snowflake, MLflow, Docker, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e01cae988d40726</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=604aae71410d0cd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f44851399d9ca9c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Oracle Database Admin - SQL/ETL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98c02d78578a5ad2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12b173b727a3ca11</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc884aee2d07d0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-19.xlsx
+++ b/results/job_matches_2026-09-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Oshkosh Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc628f7d74985c07</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8a157769951a90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b682d21992aa0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc628f7d74985c07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>OCTO ETL Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, dbt, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c291a59e036015</t>
+          <t>https://www.indeed.com/viewjob?jk=7034ddc05a5e196a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCTO ETL Data Engineer</t>
+          <t>Senior ML Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,29 +626,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Informatica PowerCenter, Oracle, SQL Server, ETL</t>
+          <t>Kinesis, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7034ddc05a5e196a</t>
+          <t>https://www.indeed.com/viewjob?jk=41542c40ed442d87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML Data Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Core Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41542c40ed442d87</t>
+          <t>https://www.indeed.com/viewjob?jk=132e8b6500861f80</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Sr. Solutions Engineer - Digital Native Business (Strategic Accounts)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cambridge Investment Research, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Hadoop, Spark, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b168d606de0f06</t>
+          <t>https://www.indeed.com/viewjob?jk=313b8143e7e2de83</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud &amp; Infrastructure Engineer</t>
+          <t>Integration Engineer 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,40 +811,110 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe21468764e4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c3d6bc274a6930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Data Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cambridge Investment Research, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Azure, Event Hubs, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b168d606de0f06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Newity LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2fe21468764e4ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Applied Machine Learning Scientist</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Grainger</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>RDS, Databricks, Scala, Snowflake, MLflow, Docker, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e8bc884aee2d07d0</t>
         </is>
